--- a/assets/with_examples/faang_experiment.xlsx
+++ b/assets/with_examples/faang_experiment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexey/ebi_projects/faang-portal-frontend/src/assets/with_examples/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yroochun/Projects/FAANG_TEMPLATES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B9412F-CCAD-EF48-AE94-DC7251F54D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D2ACAA3-56D2-AA43-BED4-E40FA00E4396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16220" firstSheet="2" activeTab="14" xr2:uid="{58DBCFEB-F75F-A348-9496-13E962F9C8F7}"/>
+    <workbookView xWindow="28800" yWindow="600" windowWidth="38400" windowHeight="19060" activeTab="13" xr2:uid="{58DBCFEB-F75F-A348-9496-13E962F9C8F7}"/>
   </bookViews>
   <sheets>
     <sheet name="submission" sheetId="13" r:id="rId1"/>
@@ -26,12 +26,13 @@
     <sheet name="bs-seq" sheetId="6" r:id="rId11"/>
     <sheet name="em-seq" sheetId="16" r:id="rId12"/>
     <sheet name="atac-seq" sheetId="7" r:id="rId13"/>
-    <sheet name="scrna-seq" sheetId="14" r:id="rId14"/>
-    <sheet name="cage-seq" sheetId="15" r:id="rId15"/>
-    <sheet name="faang_field_values" sheetId="2" state="hidden" r:id="rId16"/>
+    <sheet name="scatac-seq" sheetId="17" r:id="rId14"/>
+    <sheet name="scrna-seq" sheetId="14" r:id="rId15"/>
+    <sheet name="cage-seq" sheetId="15" r:id="rId16"/>
+    <sheet name="faang_field_values" sheetId="2" r:id="rId17"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId17"/>
+    <externalReference r:id="rId18"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'experiment ena'!$B$1:$B$61</definedName>
@@ -52,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3105" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3192" uniqueCount="608">
   <si>
     <t>Sample Descriptor</t>
   </si>
@@ -1801,13 +1802,88 @@
   </si>
   <si>
     <t>NextSeq 2000</t>
+  </si>
+  <si>
+    <t>scRNA-seq</t>
+  </si>
+  <si>
+    <t>snATAC-seq</t>
+  </si>
+  <si>
+    <t>scATAC-seq assay type</t>
+  </si>
+  <si>
+    <t>scATAC-seq sample storage processing</t>
+  </si>
+  <si>
+    <t>AQUA-FAANG</t>
+  </si>
+  <si>
+    <t>GENE-SWitCH</t>
+  </si>
+  <si>
+    <t>BovReg</t>
+  </si>
+  <si>
+    <t>Bovine-FAANG</t>
+  </si>
+  <si>
+    <t>EFFICACE</t>
+  </si>
+  <si>
+    <t>GEroNIMO</t>
+  </si>
+  <si>
+    <t>RUMIGEN</t>
+  </si>
+  <si>
+    <t>Equine-FAANG</t>
+  </si>
+  <si>
+    <t>Holoruminant</t>
+  </si>
+  <si>
+    <t>USPIGFAANG</t>
+  </si>
+  <si>
+    <t>scATAC-seq sample storage</t>
+  </si>
+  <si>
+    <t>scATAC-seq secondary project</t>
+  </si>
+  <si>
+    <t>Transposed DNA Sequence File Read Index</t>
+  </si>
+  <si>
+    <t>Cell Barcode Read</t>
+  </si>
+  <si>
+    <t>Sample Index Read</t>
+  </si>
+  <si>
+    <t>Nuclei Acid Molecule</t>
+  </si>
+  <si>
+    <t>Nucleic Acid Source</t>
+  </si>
+  <si>
+    <t>Sequencing Method</t>
+  </si>
+  <si>
+    <t>Kit Retail Name</t>
+  </si>
+  <si>
+    <t>Kit Manufacturer</t>
+  </si>
+  <si>
+    <t>Library Construction Method</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1856,6 +1932,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9.8000000000000007"/>
+      <color theme="1"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1877,7 +1960,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1889,6 +1972,7 @@
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1909,6 +1993,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="limitedValuesList"/>
       <sheetName val="faang_field_values"/>
@@ -1954,9 +2041,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1994,7 +2081,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2100,7 +2187,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2242,7 +2329,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2251,19 +2338,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{099D7B85-2870-7F44-9DA4-846DC9F871C9}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="19.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>498</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>499</v>
       </c>
@@ -2276,7 +2363,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D38584B3-9902-4E4A-AF0D-04428F33785F}">
   <dimension ref="A1:AK2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.1640625" bestFit="1" customWidth="1"/>
@@ -2317,7 +2404,7 @@
     <col min="37" max="37" width="39" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:37">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2430,12 +2517,17 @@
         <v>148</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:37">
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="AA2" s="1"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2" xr:uid="{4F13BE38-9FE0-DA43-B2B7-8965729F8B7A}">
+      <formula1>"Tn5 tagmentation, Ligation, restricted access"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -2461,7 +2553,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4F4B06E-FD05-0A45-81D7-CD289FD919BD}">
   <dimension ref="A1:AH2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.1640625" bestFit="1" customWidth="1"/>
@@ -2499,7 +2591,7 @@
     <col min="34" max="34" width="30.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:34">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2603,7 +2695,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:34">
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -2646,7 +2738,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8CD042A-2E73-AB48-8641-C39B87E182FC}">
   <dimension ref="A1:AF4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.1640625" bestFit="1" customWidth="1"/>
@@ -2684,7 +2776,7 @@
     <col min="34" max="34" width="30.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2782,13 +2874,18 @@
         <v>577</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:32">
       <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
       <c r="AE4" s="1"/>
       <c r="AF4" s="1"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2" xr:uid="{845EE151-272D-8143-B5A2-0F3458274E9F}">
+      <formula1>"whole-genome, selected genomic regions, restricted access"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2796,7 +2893,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67F024D0-A71F-1D4F-B7B8-1935431836D0}">
   <dimension ref="A1:AB2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.1640625" bestFit="1" customWidth="1"/>
@@ -2828,7 +2925,7 @@
     <col min="28" max="28" width="18.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2914,7 +3011,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:28">
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -2949,9 +3046,210 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5F3F0A2-0F3F-D140-8D28-9CEC0151DBD6}">
+  <dimension ref="A1:AM1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="33.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="32" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="26.83203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="31" bestFit="1" customWidth="1"/>
+    <col min="30" max="39" width="31" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:39" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="AB1" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC1" s="9" t="s">
+        <v>599</v>
+      </c>
+      <c r="AD1" s="9" t="s">
+        <v>600</v>
+      </c>
+      <c r="AE1" s="9" t="s">
+        <v>601</v>
+      </c>
+      <c r="AF1" s="9" t="s">
+        <v>602</v>
+      </c>
+      <c r="AG1" s="9" t="s">
+        <v>603</v>
+      </c>
+      <c r="AH1" s="9" t="s">
+        <v>604</v>
+      </c>
+      <c r="AI1" s="9" t="s">
+        <v>605</v>
+      </c>
+      <c r="AJ1" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="AK1" s="9" t="s">
+        <v>568</v>
+      </c>
+      <c r="AL1" s="9" t="s">
+        <v>607</v>
+      </c>
+      <c r="AM1" s="9"/>
+    </row>
+  </sheetData>
+  <dataConsolidate/>
+  <dataValidations count="7">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{B13F4C4A-6BD1-DA4F-9A94-F4BB50FD2A88}">
+      <formula1>"minutes, hours, days, weeks, months, years, minute, hour, day, week, month, year, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2 P2 U2 W2" xr:uid="{8952B455-BA53-5245-A558-53D00808D12B}">
+      <formula1>"decimal degrees, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2 Y2" xr:uid="{2AEE7C2D-4829-254D-9274-E81EE2CC0BC7}">
+      <formula1>"YYYY-MM-DD, YYYY-MM, YYYY, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2" xr:uid="{2335A399-1068-E147-B715-42BAA874050D}">
+      <formula1>"SO:0001747, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2" xr:uid="{49340548-6FAB-754B-8D85-613DC273DAB9}">
+      <formula1>"R1/R3, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2" xr:uid="{84B29063-D5FA-B04D-9C6A-38816954ABC9}">
+      <formula1>"R2, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE2" xr:uid="{E4E7BC4D-6195-634D-BACD-0D57DD1C62AC}">
+      <formula1>"I1, restricted access"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9DAD5BB5-2950-0048-BD7E-9416EB636803}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$22:$R$22</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CF22FA4F-46C9-2041-A4CA-C69A37A22C65}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$23:$K$23</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7CDE2CD1-D2BB-684A-8AF3-5AF95356F669}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$24:$L$24</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2E5EB13B-2C30-F84A-9883-3C9BDA72E7E0}">
+          <x14:formula1>
+            <xm:f>faang_field_values!$C$25:$L$25</xm:f>
+          </x14:formula1>
+          <xm:sqref>F2</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{915533FD-907A-6F4D-A3D0-6F3E67DCA835}">
   <dimension ref="A1:AO1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.1640625" bestFit="1" customWidth="1"/>
@@ -2981,8 +3279,8 @@
     <col min="26" max="26" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="13.83203125" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="26" customWidth="1"/>
+    <col min="30" max="30" width="21" customWidth="1"/>
     <col min="31" max="31" width="18" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="8.1640625" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="12.6640625" bestFit="1" customWidth="1"/>
@@ -2995,7 +3293,7 @@
     <col min="41" max="41" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:41">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3121,14 +3419,37 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="7">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2" xr:uid="{4C8DC41F-363B-1A4A-9FFB-60E491A6B435}">
+      <formula1>"Smart-Seq2, Drop-Seq, 10X v1, 10X v2, 10X v3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2" xr:uid="{DBC0E0FA-04AF-F646-AF27-A5C56962B791}">
+      <formula1>"oligo-dT, random"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2" xr:uid="{FE30E2CC-BD3C-914B-BA38-2E0029F8CBCE}">
+      <formula1>"PCR, in vitro transcription, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2" xr:uid="{E58F366C-B5D3-CE4F-AA48-66D3CB62AF2E}">
+      <formula1>"3 prime tag, 5 prime tag, full-length, none, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2" xr:uid="{AB888E16-3318-3343-9FE2-C3E68A712871}">
+      <formula1>"first (antisense), second (sense), both, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2" xr:uid="{294E17B4-67BD-FF4D-9FE2-07B077D7526F}">
+      <formula1>"none, External RNA Controls Consortium (ERCC), restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AL2" xr:uid="{EBE8D388-778D-954D-9730-5D3AFBCEE867}">
+      <formula1>"sense, antisense, mate 1 sense, mate 2 sense, non-stranded, restricted access"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A2353DD-D244-1A4B-A630-CADDC4768141}">
   <dimension ref="A1:AI1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.1640625" bestFit="1" customWidth="1"/>
@@ -3166,7 +3487,7 @@
     <col min="35" max="35" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3278,12 +3599,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BFC3F93-CB0B-BF48-9B11-5793D4DCF38D}">
-  <dimension ref="A1:BC1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:BC997"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="24.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="65" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="34.33203125" bestFit="1" customWidth="1"/>
@@ -3337,7 +3658,7 @@
     <col min="54" max="54" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" ht="15.75" customHeight="1">
       <c r="A1" s="5" t="s">
         <v>83</v>
       </c>
@@ -3394,7 +3715,7 @@
       <c r="Z1" s="5"/>
       <c r="AA1" s="5"/>
     </row>
-    <row r="2" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:36" ht="15.75" customHeight="1">
       <c r="A2" t="s">
         <v>95</v>
       </c>
@@ -3429,7 +3750,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:36" ht="15.75" customHeight="1">
       <c r="A3" t="s">
         <v>104</v>
       </c>
@@ -3458,7 +3779,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:36" ht="15.75" customHeight="1">
       <c r="A4" t="s">
         <v>110</v>
       </c>
@@ -3466,8 +3787,8 @@
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="6" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" ht="15.75" customHeight="1"/>
+    <row r="6" spans="1:36" ht="15.75" customHeight="1">
       <c r="A6" t="s">
         <v>112</v>
       </c>
@@ -3481,8 +3802,8 @@
         <v>139</v>
       </c>
     </row>
-    <row r="7" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" ht="15.75" customHeight="1"/>
+    <row r="8" spans="1:36" ht="15.75" customHeight="1">
       <c r="A8" t="s">
         <v>115</v>
       </c>
@@ -3505,8 +3826,8 @@
         <v>120</v>
       </c>
     </row>
-    <row r="9" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" ht="15.75" customHeight="1"/>
+    <row r="10" spans="1:36" ht="15.75" customHeight="1">
       <c r="A10" t="s">
         <v>121</v>
       </c>
@@ -3517,8 +3838,8 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" ht="15.75" customHeight="1"/>
+    <row r="12" spans="1:36" ht="15.75" customHeight="1">
       <c r="A12" t="s">
         <v>367</v>
       </c>
@@ -3628,7 +3949,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="13" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" ht="15.75" customHeight="1">
       <c r="A13" t="s">
         <v>400</v>
       </c>
@@ -3657,7 +3978,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="14" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" ht="15.75" customHeight="1">
       <c r="A14" t="s">
         <v>407</v>
       </c>
@@ -3752,7 +4073,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="15" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" ht="15.75" customHeight="1">
       <c r="A15" t="s">
         <v>185</v>
       </c>
@@ -3760,7 +4081,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="16" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" ht="15.75" customHeight="1">
       <c r="A16" t="s">
         <v>437</v>
       </c>
@@ -3792,7 +4113,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="17" spans="1:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:55" ht="15.75" customHeight="1">
       <c r="A17" t="s">
         <v>446</v>
       </c>
@@ -3959,7 +4280,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="18" spans="1:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:55" ht="15.75" customHeight="1">
       <c r="A18" t="s">
         <v>515</v>
       </c>
@@ -3967,7 +4288,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="19" spans="1:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:55" ht="15.75" customHeight="1">
       <c r="A19" t="s">
         <v>519</v>
       </c>
@@ -4014,7 +4335,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="20" spans="1:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:55" ht="15.75" customHeight="1">
       <c r="A20" t="s">
         <v>533</v>
       </c>
@@ -4088,988 +4409,1135 @@
         <v>555</v>
       </c>
     </row>
-    <row r="21" spans="1:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="1:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="1:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:55" ht="15.75" customHeight="1"/>
+    <row r="22" spans="1:55" ht="15.75" customHeight="1">
+      <c r="A22" s="5" t="s">
+        <v>585</v>
+      </c>
+      <c r="C22" t="s">
+        <v>84</v>
+      </c>
+      <c r="D22" t="s">
+        <v>85</v>
+      </c>
+      <c r="E22" t="s">
+        <v>94</v>
+      </c>
+      <c r="F22" t="s">
+        <v>93</v>
+      </c>
+      <c r="G22" t="s">
+        <v>86</v>
+      </c>
+      <c r="H22" t="s">
+        <v>87</v>
+      </c>
+      <c r="I22" t="s">
+        <v>88</v>
+      </c>
+      <c r="J22" t="s">
+        <v>89</v>
+      </c>
+      <c r="K22" t="s">
+        <v>90</v>
+      </c>
+      <c r="L22" t="s">
+        <v>91</v>
+      </c>
+      <c r="M22" t="s">
+        <v>92</v>
+      </c>
+      <c r="N22" t="s">
+        <v>16</v>
+      </c>
+      <c r="O22" t="s">
+        <v>583</v>
+      </c>
+      <c r="P22" t="s">
+        <v>562</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>584</v>
+      </c>
+      <c r="R22" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="23" spans="1:55" ht="15.75" customHeight="1">
+      <c r="A23" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="C23" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" t="s">
+        <v>105</v>
+      </c>
+      <c r="E23" t="s">
+        <v>106</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>107</v>
+      </c>
+      <c r="H23" t="s">
+        <v>108</v>
+      </c>
+      <c r="I23" t="s">
+        <v>109</v>
+      </c>
+      <c r="J23" t="s">
+        <v>98</v>
+      </c>
+      <c r="K23" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="24" spans="1:55" ht="15.75" customHeight="1">
+      <c r="A24" s="5" t="s">
+        <v>598</v>
+      </c>
+      <c r="C24" t="s">
+        <v>587</v>
+      </c>
+      <c r="D24" t="s">
+        <v>588</v>
+      </c>
+      <c r="E24" t="s">
+        <v>589</v>
+      </c>
+      <c r="F24" t="s">
+        <v>590</v>
+      </c>
+      <c r="G24" t="s">
+        <v>591</v>
+      </c>
+      <c r="H24" t="s">
+        <v>592</v>
+      </c>
+      <c r="I24" t="s">
+        <v>593</v>
+      </c>
+      <c r="J24" t="s">
+        <v>594</v>
+      </c>
+      <c r="K24" t="s">
+        <v>595</v>
+      </c>
+      <c r="L24" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="25" spans="1:55" ht="15.75" customHeight="1">
+      <c r="A25" s="5" t="s">
+        <v>597</v>
+      </c>
+      <c r="C25" t="s">
+        <v>96</v>
+      </c>
+      <c r="D25" t="s">
+        <v>97</v>
+      </c>
+      <c r="E25" t="s">
+        <v>98</v>
+      </c>
+      <c r="F25" t="s">
+        <v>99</v>
+      </c>
+      <c r="G25" t="s">
+        <v>32</v>
+      </c>
+      <c r="H25" t="s">
+        <v>100</v>
+      </c>
+      <c r="I25" t="s">
+        <v>101</v>
+      </c>
+      <c r="J25" t="s">
+        <v>102</v>
+      </c>
+      <c r="K25" t="s">
+        <v>17</v>
+      </c>
+      <c r="L25" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="26" spans="1:55" ht="15.75" customHeight="1"/>
+    <row r="27" spans="1:55" ht="15.75" customHeight="1"/>
+    <row r="28" spans="1:55" ht="15.75" customHeight="1"/>
+    <row r="29" spans="1:55" ht="15.75" customHeight="1"/>
+    <row r="30" spans="1:55" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:55" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:55" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="eZBtlJ1bg3jSagrfqOKVQfCg1QBQvhuEM5p2K1uAA3mXt2o7R/ci0PjO2kmE8iajIOEcEWV0V88Br2bd3bU+Pg==" saltValue="EJdY4IQxZAJ7XPr4nTzgqQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5077,7 +5545,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45D9D0EF-48E8-0848-8FC3-887221A9CD61}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="19.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="38.1640625" bestFit="1" customWidth="1"/>
@@ -5085,7 +5553,7 @@
     <col min="4" max="4" width="255.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>157</v>
       </c>
@@ -5099,7 +5567,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>161</v>
       </c>
@@ -5133,7 +5601,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75EBC70-0652-FD45-91E3-795D61059D70}">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -5149,7 +5617,7 @@
     <col min="12" max="12" width="13.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>498</v>
       </c>
@@ -5187,7 +5655,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
         <v>511</v>
       </c>
@@ -5257,7 +5725,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F098638-7041-8742-A382-2ACA2B20888B}">
   <dimension ref="A1:O61"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.83203125" bestFit="1" customWidth="1"/>
@@ -5276,7 +5744,7 @@
     <col min="15" max="15" width="17.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5323,7 +5791,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
         <v>15</v>
       </c>
@@ -5370,7 +5838,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15">
       <c r="A3" s="2" t="s">
         <v>27</v>
       </c>
@@ -5417,7 +5885,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15">
       <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
@@ -5464,7 +5932,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15">
       <c r="A5" s="2" t="s">
         <v>29</v>
       </c>
@@ -5511,7 +5979,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15">
       <c r="A6" s="2" t="s">
         <v>30</v>
       </c>
@@ -5558,7 +6026,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15">
       <c r="A7" s="2" t="s">
         <v>31</v>
       </c>
@@ -5605,7 +6073,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15">
       <c r="A8" s="2" t="s">
         <v>34</v>
       </c>
@@ -5652,7 +6120,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15">
       <c r="A9" s="2" t="s">
         <v>35</v>
       </c>
@@ -5699,7 +6167,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15">
       <c r="A10" s="2" t="s">
         <v>36</v>
       </c>
@@ -5746,7 +6214,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15">
       <c r="A11" s="2" t="s">
         <v>37</v>
       </c>
@@ -5793,7 +6261,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15">
       <c r="A12" s="2" t="s">
         <v>38</v>
       </c>
@@ -5840,7 +6308,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15">
       <c r="A13" s="2" t="s">
         <v>39</v>
       </c>
@@ -5887,7 +6355,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15">
       <c r="A14" s="2" t="s">
         <v>40</v>
       </c>
@@ -5934,7 +6402,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15">
       <c r="A15" s="2" t="s">
         <v>41</v>
       </c>
@@ -5981,7 +6449,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15">
       <c r="A16" s="2" t="s">
         <v>42</v>
       </c>
@@ -6028,7 +6496,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15">
       <c r="A17" s="2" t="s">
         <v>43</v>
       </c>
@@ -6075,7 +6543,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15">
       <c r="A18" s="2" t="s">
         <v>44</v>
       </c>
@@ -6122,7 +6590,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15">
       <c r="A19" s="2" t="s">
         <v>45</v>
       </c>
@@ -6169,7 +6637,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15">
       <c r="A20" s="2" t="s">
         <v>46</v>
       </c>
@@ -6216,7 +6684,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15">
       <c r="A21" s="2" t="s">
         <v>47</v>
       </c>
@@ -6263,7 +6731,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15">
       <c r="A22" s="2" t="s">
         <v>48</v>
       </c>
@@ -6310,7 +6778,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15">
       <c r="A23" s="2" t="s">
         <v>49</v>
       </c>
@@ -6357,7 +6825,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15">
       <c r="A24" s="2" t="s">
         <v>50</v>
       </c>
@@ -6404,7 +6872,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15">
       <c r="A25" s="2" t="s">
         <v>29</v>
       </c>
@@ -6451,7 +6919,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15">
       <c r="A26" s="2" t="s">
         <v>51</v>
       </c>
@@ -6498,7 +6966,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15">
       <c r="A27" s="2" t="s">
         <v>38</v>
       </c>
@@ -6545,7 +7013,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15">
       <c r="A28" s="2" t="s">
         <v>40</v>
       </c>
@@ -6592,7 +7060,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15">
       <c r="A29" s="2" t="s">
         <v>43</v>
       </c>
@@ -6639,7 +7107,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15">
       <c r="A30" s="2" t="s">
         <v>44</v>
       </c>
@@ -6686,7 +7154,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15">
       <c r="A31" s="2" t="s">
         <v>45</v>
       </c>
@@ -6733,7 +7201,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15">
       <c r="A32" s="2" t="s">
         <v>52</v>
       </c>
@@ -6780,7 +7248,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15">
       <c r="A33" s="2" t="s">
         <v>54</v>
       </c>
@@ -6827,7 +7295,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15">
       <c r="A34" s="2" t="s">
         <v>55</v>
       </c>
@@ -6874,7 +7342,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15">
       <c r="A35" s="2" t="s">
         <v>56</v>
       </c>
@@ -6921,7 +7389,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15">
       <c r="A36" s="2" t="s">
         <v>57</v>
       </c>
@@ -6968,7 +7436,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15">
       <c r="A37" s="2" t="s">
         <v>58</v>
       </c>
@@ -7015,7 +7483,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15">
       <c r="A38" s="2" t="s">
         <v>59</v>
       </c>
@@ -7062,7 +7530,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15">
       <c r="A39" s="2" t="s">
         <v>60</v>
       </c>
@@ -7109,7 +7577,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:15">
       <c r="A40" s="2" t="s">
         <v>61</v>
       </c>
@@ -7156,7 +7624,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:15">
       <c r="A41" s="2" t="s">
         <v>62</v>
       </c>
@@ -7203,7 +7671,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:15">
       <c r="A42" s="2" t="s">
         <v>63</v>
       </c>
@@ -7250,7 +7718,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:15">
       <c r="A43" s="2" t="s">
         <v>64</v>
       </c>
@@ -7297,7 +7765,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:15">
       <c r="A44" s="2" t="s">
         <v>65</v>
       </c>
@@ -7344,7 +7812,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:15">
       <c r="A45" s="2" t="s">
         <v>66</v>
       </c>
@@ -7391,7 +7859,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:15">
       <c r="A46" s="2" t="s">
         <v>67</v>
       </c>
@@ -7438,7 +7906,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:15">
       <c r="A47" s="2" t="s">
         <v>68</v>
       </c>
@@ -7485,7 +7953,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:15">
       <c r="A48" s="2" t="s">
         <v>69</v>
       </c>
@@ -7532,7 +8000,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:15">
       <c r="A49" s="2" t="s">
         <v>70</v>
       </c>
@@ -7579,7 +8047,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:15">
       <c r="A50" s="2" t="s">
         <v>71</v>
       </c>
@@ -7626,7 +8094,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:15">
       <c r="A51" s="2" t="s">
         <v>72</v>
       </c>
@@ -7673,7 +8141,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:15">
       <c r="A52" s="2" t="s">
         <v>73</v>
       </c>
@@ -7720,7 +8188,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:15">
       <c r="A53" s="2" t="s">
         <v>74</v>
       </c>
@@ -7767,7 +8235,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:15">
       <c r="A54" s="2" t="s">
         <v>75</v>
       </c>
@@ -7814,7 +8282,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:15">
       <c r="A55" s="2" t="s">
         <v>76</v>
       </c>
@@ -7861,7 +8329,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:15">
       <c r="A56" s="2" t="s">
         <v>77</v>
       </c>
@@ -7908,7 +8376,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:15">
       <c r="A57" s="2" t="s">
         <v>78</v>
       </c>
@@ -7955,7 +8423,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:15">
       <c r="A58" s="2" t="s">
         <v>79</v>
       </c>
@@ -8002,7 +8470,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:15">
       <c r="A59" s="2" t="s">
         <v>80</v>
       </c>
@@ -8049,7 +8517,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:15">
       <c r="A60" s="2" t="s">
         <v>81</v>
       </c>
@@ -8096,7 +8564,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:15">
       <c r="A61" s="2" t="s">
         <v>82</v>
       </c>
@@ -8200,7 +8668,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83A64CF7-9397-CE4E-90CF-9FB7735D75EC}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.1640625" bestFit="1" customWidth="1"/>
@@ -8234,7 +8702,7 @@
     <col min="30" max="30" width="14.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:30">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8326,12 +8794,17 @@
         <v>134</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30">
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2" xr:uid="{95AC9D10-AA72-0A4F-A232-3FDF91F98DB5}">
+      <formula1>"reduced representation, none"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -8369,7 +8842,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15FFCCF9-4CDE-C54B-AD24-35A7E281B9D4}">
   <dimension ref="A1:AJ61"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.83203125" bestFit="1" customWidth="1"/>
@@ -8404,7 +8877,7 @@
     <col min="36" max="36" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8514,7 +8987,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:36">
       <c r="A2" s="2" t="s">
         <v>15</v>
       </c>
@@ -8622,7 +9095,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:36">
       <c r="A3" s="2" t="s">
         <v>27</v>
       </c>
@@ -8730,7 +9203,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:36">
       <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
@@ -8838,7 +9311,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36">
       <c r="A5" s="2" t="s">
         <v>29</v>
       </c>
@@ -8946,7 +9419,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36">
       <c r="A6" s="2" t="s">
         <v>30</v>
       </c>
@@ -9054,7 +9527,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36">
       <c r="A7" s="2" t="s">
         <v>31</v>
       </c>
@@ -9162,7 +9635,7 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36">
       <c r="A8" s="2" t="s">
         <v>34</v>
       </c>
@@ -9270,7 +9743,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36">
       <c r="A9" s="2" t="s">
         <v>35</v>
       </c>
@@ -9378,7 +9851,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36">
       <c r="A10" s="2" t="s">
         <v>36</v>
       </c>
@@ -9486,7 +9959,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36">
       <c r="A11" s="2" t="s">
         <v>37</v>
       </c>
@@ -9594,7 +10067,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36">
       <c r="A12" s="2" t="s">
         <v>38</v>
       </c>
@@ -9702,7 +10175,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36">
       <c r="A13" s="2" t="s">
         <v>39</v>
       </c>
@@ -9810,7 +10283,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36">
       <c r="A14" s="2" t="s">
         <v>40</v>
       </c>
@@ -9918,7 +10391,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36">
       <c r="A15" s="2" t="s">
         <v>41</v>
       </c>
@@ -10026,7 +10499,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36">
       <c r="A16" s="2" t="s">
         <v>42</v>
       </c>
@@ -10134,7 +10607,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:36">
       <c r="A17" s="2" t="s">
         <v>43</v>
       </c>
@@ -10242,7 +10715,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:36">
       <c r="A18" s="2" t="s">
         <v>44</v>
       </c>
@@ -10350,7 +10823,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:36">
       <c r="A19" s="2" t="s">
         <v>45</v>
       </c>
@@ -10458,7 +10931,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:36">
       <c r="A20" s="2" t="s">
         <v>46</v>
       </c>
@@ -10566,7 +11039,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:36">
       <c r="A21" s="2" t="s">
         <v>47</v>
       </c>
@@ -10674,7 +11147,7 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:36">
       <c r="A22" s="2" t="s">
         <v>48</v>
       </c>
@@ -10782,7 +11255,7 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:36">
       <c r="A23" s="2" t="s">
         <v>49</v>
       </c>
@@ -10890,7 +11363,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:36">
       <c r="A24" s="2" t="s">
         <v>50</v>
       </c>
@@ -10998,7 +11471,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:36">
       <c r="A25" s="2" t="s">
         <v>29</v>
       </c>
@@ -11106,7 +11579,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:36">
       <c r="A26" s="2" t="s">
         <v>51</v>
       </c>
@@ -11214,7 +11687,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:36">
       <c r="A27" s="2" t="s">
         <v>38</v>
       </c>
@@ -11322,7 +11795,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:36">
       <c r="A28" s="2" t="s">
         <v>40</v>
       </c>
@@ -11430,7 +11903,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:36">
       <c r="A29" s="2" t="s">
         <v>43</v>
       </c>
@@ -11538,7 +12011,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:36">
       <c r="A30" s="2" t="s">
         <v>44</v>
       </c>
@@ -11646,7 +12119,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:36">
       <c r="A31" s="2" t="s">
         <v>45</v>
       </c>
@@ -11754,7 +12227,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:36">
       <c r="A32" s="2" t="s">
         <v>52</v>
       </c>
@@ -11862,7 +12335,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:36">
       <c r="A33" s="2" t="s">
         <v>54</v>
       </c>
@@ -11970,7 +12443,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="34" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:36">
       <c r="A34" s="2" t="s">
         <v>55</v>
       </c>
@@ -12078,7 +12551,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="35" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:36">
       <c r="A35" s="2" t="s">
         <v>56</v>
       </c>
@@ -12186,7 +12659,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="36" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:36">
       <c r="A36" s="2" t="s">
         <v>57</v>
       </c>
@@ -12294,7 +12767,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="37" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:36">
       <c r="A37" s="2" t="s">
         <v>58</v>
       </c>
@@ -12402,7 +12875,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="38" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:36">
       <c r="A38" s="2" t="s">
         <v>59</v>
       </c>
@@ -12510,7 +12983,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="39" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:36">
       <c r="A39" s="2" t="s">
         <v>60</v>
       </c>
@@ -12618,7 +13091,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="40" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:36">
       <c r="A40" s="2" t="s">
         <v>61</v>
       </c>
@@ -12726,7 +13199,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="41" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:36">
       <c r="A41" s="2" t="s">
         <v>62</v>
       </c>
@@ -12834,7 +13307,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="42" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:36">
       <c r="A42" s="2" t="s">
         <v>63</v>
       </c>
@@ -12942,7 +13415,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="43" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:36">
       <c r="A43" s="2" t="s">
         <v>64</v>
       </c>
@@ -13050,7 +13523,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="44" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:36">
       <c r="A44" s="2" t="s">
         <v>65</v>
       </c>
@@ -13158,7 +13631,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="45" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:36">
       <c r="A45" s="2" t="s">
         <v>66</v>
       </c>
@@ -13266,7 +13739,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="46" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:36">
       <c r="A46" s="2" t="s">
         <v>67</v>
       </c>
@@ -13374,7 +13847,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="47" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:36">
       <c r="A47" s="2" t="s">
         <v>68</v>
       </c>
@@ -13482,7 +13955,7 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="48" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:36">
       <c r="A48" s="2" t="s">
         <v>69</v>
       </c>
@@ -13590,7 +14063,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="49" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:36">
       <c r="A49" s="2" t="s">
         <v>70</v>
       </c>
@@ -13698,7 +14171,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:36">
       <c r="A50" s="2" t="s">
         <v>71</v>
       </c>
@@ -13806,7 +14279,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="51" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:36">
       <c r="A51" s="2" t="s">
         <v>72</v>
       </c>
@@ -13914,7 +14387,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:36">
       <c r="A52" s="2" t="s">
         <v>73</v>
       </c>
@@ -14022,7 +14495,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="53" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:36">
       <c r="A53" s="2" t="s">
         <v>74</v>
       </c>
@@ -14130,7 +14603,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:36">
       <c r="A54" s="2" t="s">
         <v>75</v>
       </c>
@@ -14238,7 +14711,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="55" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:36">
       <c r="A55" s="2" t="s">
         <v>76</v>
       </c>
@@ -14346,7 +14819,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="56" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:36">
       <c r="A56" s="2" t="s">
         <v>77</v>
       </c>
@@ -14454,7 +14927,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="57" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:36">
       <c r="A57" s="2" t="s">
         <v>78</v>
       </c>
@@ -14562,7 +15035,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="58" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:36">
       <c r="A58" s="2" t="s">
         <v>79</v>
       </c>
@@ -14670,7 +15143,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="59" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:36">
       <c r="A59" s="2" t="s">
         <v>80</v>
       </c>
@@ -14778,7 +15251,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:36">
       <c r="A60" s="2" t="s">
         <v>81</v>
       </c>
@@ -14886,7 +15359,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="61" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:36">
       <c r="A61" s="2" t="s">
         <v>82</v>
       </c>
@@ -15462,7 +15935,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{406AA4AD-A9F2-684E-89D7-0B0303DBBB91}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.1640625" bestFit="1" customWidth="1"/>
@@ -15496,7 +15969,7 @@
     <col min="30" max="30" width="11.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:30">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -15588,7 +16061,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30">
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -15625,7 +16098,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC7681A6-8E41-9842-885B-F7FC7045D433}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.1640625" bestFit="1" customWidth="1"/>
@@ -15658,7 +16131,7 @@
     <col min="29" max="29" width="11.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:30">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -15746,7 +16219,7 @@
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30">
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -15783,7 +16256,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0BD49F3-4725-E748-A029-B6B285E09FD7}">
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.1640625" bestFit="1" customWidth="1"/>
@@ -15818,7 +16291,7 @@
     <col min="31" max="31" width="39" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -15913,13 +16386,18 @@
         <v>148</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:31">
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="AA2" s="1"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2" xr:uid="{9FEAF58E-5FA8-7647-9622-3CF659A8C882}">
+      <formula1>"Tn5 tagmentation, Ligation, restricted access"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">

--- a/assets/with_examples/faang_experiment.xlsx
+++ b/assets/with_examples/faang_experiment.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yroochun/Projects/FAANG_TEMPLATES/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yroochun/Projects/faang-validator-frontend/assets/with_examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D2ACAA3-56D2-AA43-BED4-E40FA00E4396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{787F39FA-7430-674C-A125-FB454485ABE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="600" windowWidth="38400" windowHeight="19060" activeTab="13" xr2:uid="{58DBCFEB-F75F-A348-9496-13E962F9C8F7}"/>
+    <workbookView xWindow="28800" yWindow="0" windowWidth="38400" windowHeight="21600" activeTab="16" xr2:uid="{58DBCFEB-F75F-A348-9496-13E962F9C8F7}"/>
   </bookViews>
   <sheets>
     <sheet name="submission" sheetId="13" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3192" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3178" uniqueCount="607">
   <si>
     <t>Sample Descriptor</t>
   </si>
@@ -1808,9 +1808,6 @@
   </si>
   <si>
     <t>snATAC-seq</t>
-  </si>
-  <si>
-    <t>scATAC-seq assay type</t>
   </si>
   <si>
     <t>scATAC-seq sample storage processing</t>
@@ -2518,35 +2515,26 @@
       </c>
     </row>
     <row r="2" spans="1:37">
+      <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
       <c r="AA2" s="1"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2" xr:uid="{4F13BE38-9FE0-DA43-B2B7-8965729F8B7A}">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2" xr:uid="{3B507179-B437-8342-A7A5-192EF840C047}">
       <formula1>"Tn5 tagmentation, Ligation, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2 Y2" xr:uid="{A1AE72EE-245A-DE4F-9F7F-C0127C340A29}">
+      <formula1>"YYYY-MM-DD, YYYY-MM, YYYY, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2 P2 U2 W2" xr:uid="{58E16D6C-0764-CF4A-A3C3-9E2FABEDB5A6}">
+      <formula1>"decimal degrees, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{CBF6320F-EE4F-4149-9D52-7F835ECEE632}">
+      <formula1>"minutes, hours, days, weeks, months, years, minute, hour, day, week, month, year, restricted access"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{EA15EFDE-C0AF-3048-8AF7-BDF3DA1099D3}">
-          <x14:formula1>
-            <xm:f>faang_field_values!$C$2:$L$2</xm:f>
-          </x14:formula1>
-          <xm:sqref>F2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{149ADD08-0675-8F41-AA5B-1434A15C4AB5}">
-          <x14:formula1>
-            <xm:f>faang_field_values!$C$3:$J$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>G2</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -2698,40 +2686,20 @@
     <row r="2" spans="1:34">
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2 Y2" xr:uid="{5680A627-2776-D94C-9CCB-C76C898D02FD}">
+      <formula1>"YYYY-MM-DD, YYYY-MM, YYYY, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2 P2 U2 W2" xr:uid="{435EFD09-ACF3-7B4C-9893-48A1764FD6E4}">
+      <formula1>"decimal degrees, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{D78B5461-41B4-DC49-939F-CBB6971D11FA}">
+      <formula1>"minutes, hours, days, weeks, months, years, minute, hour, day, week, month, year, restricted access"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{C460B755-FA9F-7840-99D5-541E618B4DE1}">
-          <x14:formula1>
-            <xm:f>faang_field_values!$C$3:$J$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>G2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{043F7D34-6A6D-F84C-858C-9D21F12EA23D}">
-          <x14:formula1>
-            <xm:f>faang_field_values!$C$2:$L$2</xm:f>
-          </x14:formula1>
-          <xm:sqref>F2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8A075E93-1E3B-3E4E-8365-12FF7E80486B}">
-          <x14:formula1>
-            <xm:f>faang_field_values!$C$1:$N$1</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3BE31F8C-5951-2C4A-9A49-31FE38509A2D}">
-          <x14:formula1>
-            <xm:f>faang_field_values!$C$6:$E$6</xm:f>
-          </x14:formula1>
-          <xm:sqref>AB2</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -2874,6 +2842,9 @@
         <v>577</v>
       </c>
     </row>
+    <row r="2" spans="1:32">
+      <c r="E2" s="2"/>
+    </row>
     <row r="4" spans="1:32">
       <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
@@ -2881,9 +2852,18 @@
       <c r="AF4" s="1"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2" xr:uid="{845EE151-272D-8143-B5A2-0F3458274E9F}">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2" xr:uid="{AFF9C1FD-C70F-A740-AEB8-1D361944DEAF}">
       <formula1>"whole-genome, selected genomic regions, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2 Y2" xr:uid="{F3029012-CFFF-924D-8D16-00807804E3E8}">
+      <formula1>"YYYY-MM-DD, YYYY-MM, YYYY, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2 P2 U2 W2" xr:uid="{433DD1FA-33AD-DE4A-B935-B454B9D70B95}">
+      <formula1>"decimal degrees, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{996262FC-BC35-3F46-BB97-5EEE35C294B8}">
+      <formula1>"minutes, hours, days, weeks, months, years, minute, hour, day, week, month, year, restricted access"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3014,34 +2994,20 @@
     <row r="2" spans="1:28">
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2 Y2" xr:uid="{1C4D908A-90E3-4945-ACF6-57805BEEDC93}">
+      <formula1>"YYYY-MM-DD, YYYY-MM, YYYY, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2 P2 U2 W2" xr:uid="{E8C171D8-EF2A-9E44-A8F8-AAC41B5A895B}">
+      <formula1>"decimal degrees, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{5F99254D-1136-4B45-8CB4-3F8C4967B709}">
+      <formula1>"minutes, hours, days, weeks, months, years, minute, hour, day, week, month, year, restricted access"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{3F11DC62-E35E-5648-B844-5543DDBC83A1}">
-          <x14:formula1>
-            <xm:f>faang_field_values!$C$3:$J$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>G2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{8E8680DA-052A-464F-8853-7A707E219755}">
-          <x14:formula1>
-            <xm:f>faang_field_values!$C$2:$L$2</xm:f>
-          </x14:formula1>
-          <xm:sqref>F2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D90F9425-0FCF-3F42-B5AD-EB00FB185850}">
-          <x14:formula1>
-            <xm:f>faang_field_values!$C$1:$N$1</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -3155,34 +3121,34 @@
         <v>145</v>
       </c>
       <c r="AC1" s="9" t="s">
+        <v>598</v>
+      </c>
+      <c r="AD1" s="9" t="s">
         <v>599</v>
       </c>
-      <c r="AD1" s="9" t="s">
+      <c r="AE1" s="9" t="s">
         <v>600</v>
       </c>
-      <c r="AE1" s="9" t="s">
+      <c r="AF1" s="9" t="s">
         <v>601</v>
       </c>
-      <c r="AF1" s="9" t="s">
+      <c r="AG1" s="9" t="s">
         <v>602</v>
       </c>
-      <c r="AG1" s="9" t="s">
+      <c r="AH1" s="9" t="s">
         <v>603</v>
       </c>
-      <c r="AH1" s="9" t="s">
+      <c r="AI1" s="9" t="s">
         <v>604</v>
       </c>
-      <c r="AI1" s="9" t="s">
+      <c r="AJ1" s="9" t="s">
         <v>605</v>
-      </c>
-      <c r="AJ1" s="9" t="s">
-        <v>606</v>
       </c>
       <c r="AK1" s="9" t="s">
         <v>568</v>
       </c>
       <c r="AL1" s="9" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AM1" s="9"/>
     </row>
@@ -3248,7 +3214,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{915533FD-907A-6F4D-A3D0-6F3E67DCA835}">
-  <dimension ref="A1:AO1"/>
+  <dimension ref="A1:AO2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
@@ -3418,28 +3384,40 @@
         <v>131</v>
       </c>
     </row>
+    <row r="2" spans="1:41">
+      <c r="E2" s="2"/>
+    </row>
   </sheetData>
-  <dataValidations count="7">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2" xr:uid="{4C8DC41F-363B-1A4A-9FFB-60E491A6B435}">
+  <dataValidations count="10">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2" xr:uid="{C627A8BC-D657-134B-9492-9350B6472EA0}">
       <formula1>"Smart-Seq2, Drop-Seq, 10X v1, 10X v2, 10X v3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2" xr:uid="{DBC0E0FA-04AF-F646-AF27-A5C56962B791}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2" xr:uid="{A6985C99-738D-5444-985D-6372F2E1206C}">
       <formula1>"oligo-dT, random"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2" xr:uid="{FE30E2CC-BD3C-914B-BA38-2E0029F8CBCE}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2" xr:uid="{433179F2-40A6-3C47-A8E1-E2189E3BD72D}">
       <formula1>"PCR, in vitro transcription, not collected, not provided, restricted access"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2" xr:uid="{E58F366C-B5D3-CE4F-AA48-66D3CB62AF2E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2" xr:uid="{DEC62A85-EB73-384A-9ADD-F0725EE72EB3}">
       <formula1>"3 prime tag, 5 prime tag, full-length, none, restricted access"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2" xr:uid="{AB888E16-3318-3343-9FE2-C3E68A712871}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2" xr:uid="{3CA1A1FD-4E17-C941-A57C-C881CE9F9B4D}">
       <formula1>"first (antisense), second (sense), both, restricted access"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2" xr:uid="{294E17B4-67BD-FF4D-9FE2-07B077D7526F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2" xr:uid="{0CAA2EF9-EB36-5746-93ED-B46B4CFD8F74}">
       <formula1>"none, External RNA Controls Consortium (ERCC), restricted access"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AL2" xr:uid="{EBE8D388-778D-954D-9730-5D3AFBCEE867}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AL2" xr:uid="{3856FC16-09D6-384A-8778-6FB88EE60234}">
       <formula1>"sense, antisense, mate 1 sense, mate 2 sense, non-stranded, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2 Y2" xr:uid="{1F7D3350-E8E3-DE48-A000-0FE956D358D5}">
+      <formula1>"YYYY-MM-DD, YYYY-MM, YYYY, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2 P2 U2 W2" xr:uid="{4958079D-6288-854D-A048-6674261726E7}">
+      <formula1>"decimal degrees, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{7FC94539-BE5F-764A-B10C-8E4473050858}">
+      <formula1>"minutes, hours, days, weeks, months, years, minute, hour, day, week, month, year, restricted access"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3448,7 +3426,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A2353DD-D244-1A4B-A630-CADDC4768141}">
-  <dimension ref="A1:AI1"/>
+  <dimension ref="A1:AI2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
@@ -3594,7 +3572,21 @@
         <v>131</v>
       </c>
     </row>
+    <row r="2" spans="1:35">
+      <c r="E2" s="2"/>
+    </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2 Y2" xr:uid="{106BEC23-D9E9-8842-8C77-0DF9E1FE8EEF}">
+      <formula1>"YYYY-MM-DD, YYYY-MM, YYYY, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2 P2 U2 W2" xr:uid="{14CD941F-9F38-334D-A2B7-9A5CAF5A0A9D}">
+      <formula1>"decimal degrees, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{93EB6130-8C89-3B4E-AC9D-2F712869A120}">
+      <formula1>"minutes, hours, days, weeks, months, years, minute, hour, day, week, month, year, restricted access"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3670,41 +3662,47 @@
         <v>85</v>
       </c>
       <c r="E1" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="M1" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>94</v>
-      </c>
       <c r="O1" s="5" t="s">
+        <v>583</v>
+      </c>
+      <c r="P1" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
+      <c r="Q1" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>139</v>
+      </c>
       <c r="S1" s="5"/>
       <c r="T1" s="5"/>
       <c r="U1" s="5"/>
@@ -4411,61 +4409,11 @@
     </row>
     <row r="21" spans="1:55" ht="15.75" customHeight="1"/>
     <row r="22" spans="1:55" ht="15.75" customHeight="1">
-      <c r="A22" s="5" t="s">
-        <v>585</v>
-      </c>
-      <c r="C22" t="s">
-        <v>84</v>
-      </c>
-      <c r="D22" t="s">
-        <v>85</v>
-      </c>
-      <c r="E22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F22" t="s">
-        <v>93</v>
-      </c>
-      <c r="G22" t="s">
-        <v>86</v>
-      </c>
-      <c r="H22" t="s">
-        <v>87</v>
-      </c>
-      <c r="I22" t="s">
-        <v>88</v>
-      </c>
-      <c r="J22" t="s">
-        <v>89</v>
-      </c>
-      <c r="K22" t="s">
-        <v>90</v>
-      </c>
-      <c r="L22" t="s">
-        <v>91</v>
-      </c>
-      <c r="M22" t="s">
-        <v>92</v>
-      </c>
-      <c r="N22" t="s">
-        <v>16</v>
-      </c>
-      <c r="O22" t="s">
-        <v>583</v>
-      </c>
-      <c r="P22" t="s">
-        <v>562</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>584</v>
-      </c>
-      <c r="R22" t="s">
-        <v>139</v>
-      </c>
+      <c r="A22" s="5"/>
     </row>
     <row r="23" spans="1:55" ht="15.75" customHeight="1">
       <c r="A23" s="5" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C23" t="s">
         <v>53</v>
@@ -4497,42 +4445,42 @@
     </row>
     <row r="24" spans="1:55" ht="15.75" customHeight="1">
       <c r="A24" s="5" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C24" t="s">
+        <v>586</v>
+      </c>
+      <c r="D24" t="s">
         <v>587</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>588</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>589</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>590</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>591</v>
       </c>
-      <c r="H24" t="s">
+      <c r="I24" t="s">
         <v>592</v>
       </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>593</v>
       </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
         <v>594</v>
       </c>
-      <c r="K24" t="s">
+      <c r="L24" t="s">
         <v>595</v>
-      </c>
-      <c r="L24" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="25" spans="1:55" ht="15.75" customHeight="1">
       <c r="A25" s="5" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C25" t="s">
         <v>96</v>
@@ -4572,971 +4520,971 @@
     <row r="30" spans="1:55" ht="15.75" customHeight="1"/>
     <row r="31" spans="1:55" ht="15.75" customHeight="1"/>
     <row r="32" spans="1:55" ht="15.75" customHeight="1"/>
-    <row r="33" ht="15.75" customHeight="1"/>
-    <row r="34" ht="15.75" customHeight="1"/>
-    <row r="35" ht="15.75" customHeight="1"/>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
-    <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
-    <row r="49" ht="15.75" customHeight="1"/>
-    <row r="50" ht="15.75" customHeight="1"/>
-    <row r="51" ht="15.75" customHeight="1"/>
-    <row r="52" ht="15.75" customHeight="1"/>
-    <row r="53" ht="15.75" customHeight="1"/>
-    <row r="54" ht="15.75" customHeight="1"/>
-    <row r="55" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1"/>
-    <row r="57" ht="15.75" customHeight="1"/>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="59" ht="15.75" customHeight="1"/>
-    <row r="60" ht="15.75" customHeight="1"/>
-    <row r="61" ht="15.75" customHeight="1"/>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1"/>
-    <row r="64" ht="15.75" customHeight="1"/>
-    <row r="65" ht="15.75" customHeight="1"/>
-    <row r="66" ht="15.75" customHeight="1"/>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1"/>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1"/>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1"/>
-    <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
-    <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="33" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="34" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="35" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="36" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="37" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="38" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="39" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="40" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="41" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="42" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="43" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="44" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="45" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="46" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="47" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="48" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="49" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="50" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="51" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="52" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="53" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="54" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="55" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="56" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="57" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="58" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="59" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="60" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="61" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="62" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="63" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="64" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="65" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="66" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="67" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="68" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="69" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="70" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="71" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="72" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="73" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="74" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="75" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="76" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="77" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="78" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="79" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="80" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="81" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="82" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="83" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="84" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="85" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="86" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="87" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="88" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="89" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="90" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="91" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="92" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="93" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="94" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="95" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="96" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="97" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="98" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="99" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="100" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="101" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="102" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="103" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="104" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="105" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="106" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="107" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="108" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="109" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="110" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="111" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="112" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="113" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="114" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="115" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="116" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="117" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="118" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="119" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="120" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="121" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="122" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="123" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="124" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="125" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="126" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="127" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="128" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="129" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="130" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="131" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="132" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="133" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="134" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="135" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="136" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="137" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="138" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="139" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="140" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="141" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="142" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="143" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="144" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="145" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="146" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="147" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="148" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="149" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="150" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="151" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="152" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="153" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="154" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="155" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="156" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="157" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="158" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="159" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="160" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="161" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="162" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="163" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="164" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="165" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="166" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="167" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="168" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="169" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="170" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="171" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="172" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="173" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="174" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="175" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="176" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="177" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="178" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="179" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="180" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="181" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="182" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="183" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="184" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="185" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="186" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="187" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="188" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="189" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="190" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="191" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="192" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="193" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="194" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="195" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="196" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="197" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="198" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="199" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="200" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="201" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="202" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="203" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="204" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="205" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="206" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="207" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="208" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="209" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="210" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="211" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="212" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="213" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="214" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="215" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="216" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="217" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="218" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="219" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="220" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="221" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="222" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="223" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="224" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="225" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="226" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="227" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="228" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="229" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="230" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="231" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="232" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="233" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="234" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="235" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="236" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="237" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="238" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="239" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="240" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="241" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="242" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="243" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="244" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="245" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="246" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="247" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="248" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="249" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="250" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="251" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="252" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="253" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="254" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="255" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="256" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="257" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="258" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="259" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="260" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="261" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="262" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="263" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="264" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="265" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="266" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="267" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="268" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="269" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="270" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="271" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="272" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="273" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="274" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="275" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="276" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="277" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="278" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="279" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="280" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="281" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="282" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="283" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="284" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="285" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="286" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="287" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="288" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="289" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="290" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="291" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="292" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="293" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="294" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="295" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="296" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="297" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="298" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="299" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="300" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="301" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="302" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="303" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="304" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="305" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="306" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="307" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="308" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="309" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="310" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="311" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="312" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="313" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="314" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="315" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="316" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="317" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="318" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="319" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="320" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="321" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="322" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="323" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="324" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="325" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="326" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="327" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="328" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="329" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="330" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="331" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="332" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="333" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="334" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="335" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="336" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="337" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="338" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="339" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="340" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="341" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="342" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="343" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="344" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="345" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="346" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="347" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="348" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="349" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="350" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="351" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="352" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="353" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="354" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="355" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="356" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="357" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="358" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="359" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="360" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="361" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="362" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="363" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="364" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="365" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="366" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="367" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="368" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="369" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="370" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="371" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="372" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="373" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="374" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="375" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="376" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="377" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="378" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="379" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="380" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="381" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="382" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="383" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="384" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="385" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="386" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="387" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="388" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="389" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="390" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="391" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="392" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="393" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="394" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="395" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="396" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="397" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="398" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="399" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="400" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="401" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="402" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="403" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="404" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="405" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="406" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="407" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="408" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="409" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="410" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="411" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="412" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="413" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="414" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="415" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="416" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="417" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="418" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="419" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="420" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="421" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="422" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="423" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="424" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="425" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="426" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="427" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="428" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="429" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="430" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="431" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="432" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="433" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="434" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="435" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="436" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="437" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="438" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="439" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="440" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="441" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="442" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="443" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="444" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="445" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="446" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="447" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="448" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="449" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="450" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="451" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="452" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="453" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="454" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="455" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="456" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="457" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="458" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="459" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="460" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="461" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="462" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="463" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="464" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="465" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="466" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="467" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="468" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="469" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="470" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="471" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="472" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="473" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="474" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="475" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="476" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="477" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="478" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="479" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="480" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="481" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="482" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="483" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="484" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="485" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="486" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="487" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="488" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="489" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="490" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="491" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="492" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="493" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="494" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="495" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="496" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="497" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="498" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="499" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="500" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="501" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="502" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="503" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="504" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="505" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="506" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="507" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="508" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="509" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="510" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="511" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="512" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="513" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="514" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="515" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="516" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="517" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="518" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="519" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="520" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="521" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="522" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="523" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="524" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="525" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="526" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="527" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="528" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="529" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="530" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="531" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="532" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="533" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="534" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="535" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="536" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="537" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="538" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="539" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="540" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="541" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="542" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="543" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="544" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="545" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="546" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="547" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="548" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="549" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="550" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="551" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="552" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="553" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="554" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="555" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="556" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="557" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="558" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="559" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="560" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="561" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="562" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="563" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="564" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="565" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="566" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="567" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="568" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="569" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="570" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="571" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="572" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="573" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="574" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="575" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="576" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="577" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="578" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="579" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="580" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="581" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="582" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="583" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="584" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="585" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="586" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="587" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="588" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="589" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="590" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="591" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="592" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="593" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="594" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="595" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="596" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="597" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="598" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="599" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="600" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="601" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="602" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="603" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="604" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="605" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="606" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="607" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="608" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="609" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="610" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="611" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="612" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="613" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="614" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="615" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="616" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="617" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="618" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="619" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="620" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="621" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="622" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="623" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="624" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="625" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="626" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="627" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="628" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="629" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="630" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="631" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="632" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="633" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="634" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="635" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="636" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="637" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="638" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="639" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="640" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="641" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="642" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="643" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="644" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="645" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="646" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="647" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="648" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="649" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="650" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="651" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="652" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="653" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="654" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="655" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="656" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="657" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="658" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="659" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="660" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="661" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="662" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="663" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="664" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="665" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="666" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="667" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="668" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="669" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="670" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="671" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="672" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="673" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="674" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="675" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="676" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="677" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="678" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="679" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="680" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="681" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="682" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="683" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="684" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="685" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="686" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="687" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="688" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="689" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="690" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="691" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="692" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="693" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="694" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="695" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="696" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="697" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="698" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="699" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="700" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="701" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="702" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="703" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="704" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="705" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="706" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="707" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="708" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="709" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="710" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="711" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="712" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="713" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="714" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="715" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="716" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="717" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="718" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="719" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="720" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="721" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="722" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="723" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="724" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="725" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="726" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="727" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="728" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="729" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="730" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="731" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="732" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="733" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="734" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="735" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="736" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="737" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="738" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="739" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="740" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="741" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="742" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="743" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="744" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="745" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="746" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="747" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="748" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="749" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="750" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="751" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="752" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="753" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="754" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="755" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="756" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="757" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="758" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="759" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="760" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="761" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="762" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="763" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="764" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="765" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="766" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="767" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="768" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="769" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="770" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="771" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="772" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="773" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="774" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="775" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="776" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="777" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="778" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="779" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="780" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="781" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="782" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="783" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="784" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="785" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="786" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="787" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="788" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="789" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="790" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="791" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="792" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="793" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="794" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="795" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="796" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="797" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="798" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="799" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="800" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="801" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="802" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="803" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="804" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="805" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="806" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="807" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="808" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="809" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="810" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="811" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="812" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="813" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="814" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="815" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="816" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="817" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="818" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="819" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="820" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="821" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="822" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="823" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="824" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="825" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="826" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="827" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="828" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="829" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="830" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="831" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="832" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="833" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="834" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="835" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="836" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="837" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="838" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="839" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="840" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="841" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="842" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="843" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="844" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="845" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="846" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="847" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="848" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="849" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="850" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="851" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="852" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="853" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="854" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="855" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="856" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="857" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="858" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="859" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="860" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="861" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="862" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="863" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="864" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="865" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="866" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="867" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="868" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="869" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="870" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="871" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="872" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="873" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="874" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="875" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="876" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="877" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="878" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="879" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="880" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="881" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="882" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="883" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="884" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="885" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="886" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="887" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="888" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="889" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="890" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="891" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="892" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="893" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="894" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="895" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="896" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="897" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="898" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="899" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="900" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="901" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="902" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="903" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="904" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="905" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="906" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="907" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="908" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="909" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="910" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="911" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="912" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="913" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="914" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="915" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="916" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="917" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="918" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="919" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="920" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="921" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="922" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="923" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="924" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="925" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="926" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="927" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="928" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="929" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="930" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="931" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="932" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="933" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="934" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="935" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="936" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="937" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="938" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="939" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="940" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="941" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="942" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="943" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="944" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="945" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="946" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="947" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="948" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="949" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="950" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="951" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="952" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="953" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="954" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="955" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="956" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="957" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="958" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="959" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="960" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="961" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="962" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="963" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="964" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="965" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="966" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="967" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="968" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="969" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="970" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="971" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="972" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="973" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="974" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="975" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="976" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="977" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="978" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="979" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="980" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="981" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="982" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="983" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="984" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="985" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="986" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="987" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="988" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="989" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="990" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="991" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="992" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="993" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="994" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="995" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="996" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="997" customFormat="1" ht="15.75" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5724,7 +5672,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F098638-7041-8742-A382-2ACA2B20888B}">
-  <dimension ref="A1:O61"/>
+  <dimension ref="A1:O128"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
@@ -8611,6 +8559,70 @@
         <v>189</v>
       </c>
     </row>
+    <row r="65" customFormat="1"/>
+    <row r="66" customFormat="1"/>
+    <row r="67" customFormat="1"/>
+    <row r="68" customFormat="1"/>
+    <row r="69" customFormat="1"/>
+    <row r="70" customFormat="1"/>
+    <row r="71" customFormat="1"/>
+    <row r="72" customFormat="1"/>
+    <row r="73" customFormat="1"/>
+    <row r="74" customFormat="1"/>
+    <row r="75" customFormat="1"/>
+    <row r="76" customFormat="1"/>
+    <row r="77" customFormat="1"/>
+    <row r="78" customFormat="1"/>
+    <row r="79" customFormat="1"/>
+    <row r="80" customFormat="1"/>
+    <row r="81" customFormat="1"/>
+    <row r="82" customFormat="1"/>
+    <row r="83" customFormat="1"/>
+    <row r="84" customFormat="1"/>
+    <row r="85" customFormat="1"/>
+    <row r="86" customFormat="1"/>
+    <row r="87" customFormat="1"/>
+    <row r="88" customFormat="1"/>
+    <row r="89" customFormat="1"/>
+    <row r="90" customFormat="1"/>
+    <row r="91" customFormat="1"/>
+    <row r="92" customFormat="1"/>
+    <row r="93" customFormat="1"/>
+    <row r="94" customFormat="1"/>
+    <row r="95" customFormat="1"/>
+    <row r="96" customFormat="1"/>
+    <row r="97" customFormat="1"/>
+    <row r="98" customFormat="1"/>
+    <row r="99" customFormat="1"/>
+    <row r="100" customFormat="1"/>
+    <row r="101" customFormat="1"/>
+    <row r="102" customFormat="1"/>
+    <row r="103" customFormat="1"/>
+    <row r="104" customFormat="1"/>
+    <row r="105" customFormat="1"/>
+    <row r="106" customFormat="1"/>
+    <row r="107" customFormat="1"/>
+    <row r="108" customFormat="1"/>
+    <row r="109" customFormat="1"/>
+    <row r="110" customFormat="1"/>
+    <row r="111" customFormat="1"/>
+    <row r="112" customFormat="1"/>
+    <row r="113" customFormat="1"/>
+    <row r="114" customFormat="1"/>
+    <row r="115" customFormat="1"/>
+    <row r="116" customFormat="1"/>
+    <row r="117" customFormat="1"/>
+    <row r="118" customFormat="1"/>
+    <row r="119" customFormat="1"/>
+    <row r="120" customFormat="1"/>
+    <row r="121" customFormat="1"/>
+    <row r="122" customFormat="1"/>
+    <row r="123" customFormat="1"/>
+    <row r="124" customFormat="1"/>
+    <row r="125" customFormat="1"/>
+    <row r="126" customFormat="1"/>
+    <row r="127" customFormat="1"/>
+    <row r="128" customFormat="1"/>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8797,45 +8809,23 @@
     <row r="2" spans="1:30">
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2" xr:uid="{95AC9D10-AA72-0A4F-A232-3FDF91F98DB5}">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2" xr:uid="{E31018FA-6D20-A645-AC71-3AC202E7453A}">
       <formula1>"reduced representation, none"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2" xr:uid="{7B2A36E4-EAF3-DC44-A8FC-093CE51ACCEF}">
+      <formula1>"YYYY-MM-DD, YYYY-MM, YYYY, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2 P2 W2 U2" xr:uid="{598DED6E-C580-EB4E-B765-C557249D7F4D}">
+      <formula1>"decimal degrees, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{E6B9634E-612F-E348-966C-6224670A653E}">
+      <formula1>"minutes, hours, days, weeks, months, years, minute, hour, day, week, month, year, restricted access"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C62E301D-8248-B944-9FDB-59C9C09B8F83}">
-          <x14:formula1>
-            <xm:f>faang_field_values!$C$1:$N$1</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{14E138D7-4850-0A4C-A78C-04C49A19DC51}">
-          <x14:formula1>
-            <xm:f>faang_field_values!$C$2:$L$2</xm:f>
-          </x14:formula1>
-          <xm:sqref>F2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{635BC845-20CB-1744-BC79-5C578ABBBA5A}">
-          <x14:formula1>
-            <xm:f>faang_field_values!$C$3:$J$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>G2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BEBD69DF-17F0-D744-A345-E04E060CE5D3}">
-          <x14:formula1>
-            <xm:f>faang_field_values!$C$10:$D$10</xm:f>
-          </x14:formula1>
-          <xm:sqref>AC2</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -16067,31 +16057,18 @@
       <c r="G2" s="2"/>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2 Y2" xr:uid="{D1FCBB9E-FE62-594F-BB28-13F490BE073C}">
+      <formula1>"YYYY-MM-DD, YYYY-MM, YYYY, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2 P2 U2 W2" xr:uid="{E39518F2-BDA2-EF41-8ABE-FB819F0E465A}">
+      <formula1>"decimal degrees, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{74C406C7-226A-F341-B704-5843727C1416}">
+      <formula1>"minutes, hours, days, weeks, months, years, minute, hour, day, week, month, year, restricted access"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{B3E0CA1B-4D6D-6149-8682-9DB682EFDFE0}">
-          <x14:formula1>
-            <xm:f>faang_field_values!$C$3:$J$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>G2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{DF817772-9C8F-2343-8D1B-85370CD3BF02}">
-          <x14:formula1>
-            <xm:f>faang_field_values!$C$2:$L$2</xm:f>
-          </x14:formula1>
-          <xm:sqref>F2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{338EEE75-D370-8A4D-9140-60BFB5E3F1FF}">
-          <x14:formula1>
-            <xm:f>faang_field_values!$C$1:$N$1</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -16222,34 +16199,20 @@
     <row r="2" spans="1:30">
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2 Y2" xr:uid="{DCF4B47F-AC96-C44A-AF97-B815AAE8592E}">
+      <formula1>"YYYY-MM-DD, YYYY-MM, YYYY, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2 P2 U2 W2" xr:uid="{6280B9AD-C242-CC4A-91F2-A811D7D94D3C}">
+      <formula1>"decimal degrees, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{7FB7828F-D370-6E45-9E6C-35D7A8A6B59D}">
+      <formula1>"minutes, hours, days, weeks, months, years, minute, hour, day, week, month, year, restricted access"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8D5E3DB2-EC39-3C4F-9821-F1F8EEDE1843}">
-          <x14:formula1>
-            <xm:f>faang_field_values!$C$1:$N$1</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{403043A1-F251-7747-B9F6-B24AB7A9DD00}">
-          <x14:formula1>
-            <xm:f>faang_field_values!$C$2:$L$2</xm:f>
-          </x14:formula1>
-          <xm:sqref>F2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{18764BFC-F0B5-C742-A294-27BA360B391E}">
-          <x14:formula1>
-            <xm:f>faang_field_values!$C$3:$J$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>G2</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -16389,39 +16352,23 @@
     <row r="2" spans="1:31">
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
       <c r="AA2" s="1"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2" xr:uid="{9FEAF58E-5FA8-7647-9622-3CF659A8C882}">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2" xr:uid="{F8081C68-869E-9C4C-88D8-D17823F86768}">
       <formula1>"Tn5 tagmentation, Ligation, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2 Y2" xr:uid="{0C8D7F85-3442-AA44-B9D0-DB7B369B89E7}">
+      <formula1>"YYYY-MM-DD, YYYY-MM, YYYY, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2 N2 U2 W2" xr:uid="{8EE69A68-FA56-B446-BD23-BB1CD9D47F65}">
+      <formula1>"decimal degrees, not applicable, not collected, not provided, restricted access"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{67E85C69-0C5D-D545-9A0C-911BD46E0744}">
+      <formula1>"minutes, hours, days, weeks, months, years, minute, hour, day, week, month, year, restricted access"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{E5794F02-B71D-B847-983B-F96FCA4C0E87}">
-          <x14:formula1>
-            <xm:f>faang_field_values!$C$3:$J$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>G2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{8580A94C-226D-B947-94D3-CD9D72A3F567}">
-          <x14:formula1>
-            <xm:f>faang_field_values!$C$2:$L$2</xm:f>
-          </x14:formula1>
-          <xm:sqref>F2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EE19D93F-F23D-0B42-86C6-1CE61152BE0E}">
-          <x14:formula1>
-            <xm:f>faang_field_values!$C$1:$N$1</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>